--- a/backend/data/financials_by_company/1338.HK.xlsx
+++ b/backend/data/financials_by_company/1338.HK.xlsx
@@ -3778,10 +3778,8 @@
           <t>Guangzhou</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>510450</t>
-        </is>
+      <c r="D2" t="n">
+        <v>510450</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -3890,7 +3888,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>Infinity</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AG2" t="n">
